--- a/قائمة-الألفاظ-بل.xlsx
+++ b/قائمة-الألفاظ-بل.xlsx
@@ -10,16 +10,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="اقرأني" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الألفاظ" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأحاديث" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="حالات الامتناع" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ألفاظ خارج القائمة" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مستبعدة" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المصادر والشروط" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'الألفاظ'!$A$1:$L$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'الألفاظ'!$A$1:$O$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'الأحاديث'!$A$1:$J$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'حالات الامتناع'!$A$1:$H$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'مستبعدة'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'المصادر والشروط'!$A$1:$E$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ألفاظ خارج القائمة'!$A$1:$J$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'مستبعدة'!$A$1:$E$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'المصادر والشروط'!$A$1:$E$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -62,7 +62,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -72,11 +72,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E3D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -106,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
@@ -127,9 +122,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
@@ -497,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -514,7 +506,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>أُعدّت في 27 سبتمبر 2026، واستُكملت الألفاظ التسعة المؤجلة في 1 أكتوبر 2026، قبل أيام البناء (4–6 أكتوبر). ارفعها إلى GitHub قبل 4 أكتوبر لتُثبت أنها نسخة البداية.</t>
+          <t>أُعدّت في 27 سبتمبر 2026، واستُكملت في 1 أكتوبر 2026، وأُعيد بناؤها في 1 أكتوبر على «موسوعة التفسير» في الدرر السنية مصدراً أساسياً، لأنها ضمن المرجعية العلمية المعتمدة في «الحزمة العلمية» للتحدي.</t>
         </is>
       </c>
     </row>
@@ -531,35 +523,35 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>• «الألفاظ»: الألفاظ المعتمدة في التطبيق. لكل لفظ آيته، ومعناه منقولاً بنصه من «السراج في بيان غريب القرآن» عبر QuranEnc، والمعنى المعاصر الذي قد يُفهم خطأً (صياغة الفريق، يُستعمل خياراً خاطئاً في الاختبار فقط).</t>
+          <t>• «الألفاظ»: الألفاظ المعتمدة في التطبيق. لكل لفظ معناه منقولاً بنصه من موسوعة التفسير (الدرر السنية) مع القسم والرابط، وتحته ما يوافقه في «السراج في بيان غريب القرآن»، ثم المعنى المعاصر الذي قد يُفهم خطأً (صياغة الفريق للاختبار فقط).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>• «الأحاديث»: بطاقات «التعريف النبوي» من موسوعة الأحاديث النبوية HadeethEnc، ونص الحديث منقول كما هو.</t>
+          <t>• «الأحاديث»: بطاقات الأحاديث، مع تخريجها في الصحيحين من الموسوعة الحديثية (الدرر السنية).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>• «حالات الامتناع»: ألفاظ لا يشرحها «السراج» في موضعها. لا تدخل التطبيق، وتُستعمل في اختبار الحالات الحرجة: يجب أن يمتنع النظام ولا يخترع معنى.</t>
+          <t>• «ألفاظ خارج القائمة»: ألفاظ تشرحها الموسوعة ولا يشرحها «السراج»، فلم يتحقق فيها شرط الموافقة ولم تدخل القائمة. تُستعمل لاختبار امتناع التطبيق عن الحكم في ما ليس في قائمته.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>• «مستبعدة»: ألفاظ حُذفت لخلاف في معناها أو حساسيتها، مع سبب الحذف. تُعرض على المحكّمين دليلاً على الانضباط.</t>
+          <t>• «مستبعدة»: ألفاظ حُذفت مع سبب الحذف.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>• «المصادر والشروط»: شروط QuranEnc للاستخدام، ورقم الإصدار.</t>
+          <t>• «المصادر والشروط»: المصادر وشروط استخدامها.</t>
         </is>
       </c>
     </row>
@@ -569,96 +561,95 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>تنبيهان مهمان:</t>
+          <t>قواعد اختيار المعنى:</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>1) شروط QuranEnc تمنع أي تعديل على النص. الخلايا المظللة بالأصفر في عمود «درجة الثقة» تحتاج مطابقة بالعين مع الموقع قبل الاستخدام.</t>
+          <t>1) اللفظ في «غريب الكلمات» في موضعه: نص الموسوعة هو المعنى.  2) مشروح في موضع آخر للكلمة بالمعنى نفسه: يُنقل ذلك النص ويُذكر موضعه، ويبقى اللفظ في الآية التي يقع فيها الفهم الخاطئ.  3) ليس في «غريب الكلمات» ونص التفسير يصرّح بمعناه: تُنقل جملة التفسير بنصها مع اسم القسم.  4) الموسوعة لا تذكر المعنى، أو يخالفها «السراج»، أو لا يؤيد معناها أن الفهم الشائع خطأ: يُستبعد اللفظ.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2) في التطبيق، الأفضل أن يُجلب المعنى مباشرة من QuranEnc وقت التشغيل، وتبقى هذه القائمة فهرساً ونسخة مرجعية.</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>طريقة النقل:</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>نُقل كل نص من الموسوعة مرتين أو ثلاثاً وقورنت النسخ، وحُذفت أرقام الحواشي وإحالاتها («يُنظر: ...») والنقطة الأخيرة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>ملخص:</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>عدد الألفاظ المعتمدة</t>
         </is>
       </c>
-      <c r="B16" s="4">
+      <c r="B18" s="4">
         <f>COUNTA('الألفاظ'!B2:B200)</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>منها من جزء عمّ</t>
-        </is>
-      </c>
-      <c r="B17" s="4">
-        <f>COUNTIF('الألفاظ'!H2:H200,"نعم")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>منها تحتاج مطابقة بالعين</t>
-        </is>
-      </c>
-      <c r="B18" s="4">
-        <f>COUNTA('الألفاظ'!I2:I200)-COUNTIF('الألفاظ'!I2:I200,"عالية:*")</f>
-        <v/>
-      </c>
-    </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>منها من جزء عمّ</t>
+        </is>
+      </c>
+      <c r="B19" s="4">
+        <f>COUNTIF('الألفاظ'!M2:M200,"نعم")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>بطاقات الأحاديث</t>
         </is>
       </c>
-      <c r="B19" s="4">
+      <c r="B20" s="4">
         <f>COUNTA('الأحاديث'!B2:B50)</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>حالات الامتناع (للاختبار)</t>
-        </is>
-      </c>
-      <c r="B20" s="4">
-        <f>COUNTA('حالات الامتناع'!B2:B50)</f>
-        <v/>
-      </c>
-    </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>ألفاظ خارج القائمة (للاختبار)</t>
+        </is>
+      </c>
+      <c r="B21" s="4">
+        <f>COUNTA('ألفاظ خارج القائمة'!B2:B50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>ألفاظ مستبعدة</t>
         </is>
       </c>
-      <c r="B21" s="4">
+      <c r="B22" s="4">
         <f>COUNTA('مستبعدة'!B2:B50)</f>
         <v/>
       </c>
@@ -674,21 +665,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
-    <col width="42" customWidth="1" min="12" max="12"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -699,7 +693,7 @@
       </c>
       <c r="B1" s="5" t="inlineStr">
         <is>
-          <t>اللفظ (كما في المصدر)</t>
+          <t>اللفظ</t>
         </is>
       </c>
       <c r="C1" s="5" t="inlineStr">
@@ -719,37 +713,52 @@
       </c>
       <c r="F1" s="5" t="inlineStr">
         <is>
+          <t>المعنى في موسوعة التفسير (منقول بنصه)</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>قسم الموسوعة</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>موضع الشرح في الموسوعة (إن اختلف)</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>رابط الموسوعة</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
           <t>المعنى في «السراج» (منقول بنصه)</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>علاقة «السراج» بالموسوعة</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>المعنى المعاصر الذي قد يُفهم خطأً (صياغة الفريق — للاختبار فقط)</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>جزء عمّ</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
-        <is>
-          <t>درجة الثقة في النقل</t>
-        </is>
-      </c>
-      <c r="J1" s="5" t="inlineStr">
-        <is>
-          <t>مصدر إدراج اللفظ</t>
-        </is>
-      </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>ملاحظات</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
-        <is>
-          <t>رابط التحقق (الآية في صفحة السورة)</t>
+      <c r="O1" s="5" t="inlineStr">
+        <is>
+          <t>رابط «السراج»</t>
         </is>
       </c>
     </row>
@@ -775,27 +784,38 @@
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
+          <t>وهؤلاءِ الخاشعون هم الموقِنون بعودتهم إلى الله تعالى، والحشرِ إليه يوم القِيامة</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>تفسير الآيات</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr"/>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>https://dorar.net/tafseer/2/8</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
           <t>يَظُنُّونَ: يُوقِنُونَ.</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>يشكّون ويتوقعون</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr"/>
-      <c r="I2" s="8" t="inlineStr">
-        <is>
-          <t>متوسطة: الحروف متسقة، والحركات تحتاج مطابقة بالعين</t>
-        </is>
-      </c>
-      <c r="J2" s="7" t="inlineStr">
-        <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K2" s="7" t="inlineStr"/>
-      <c r="L2" s="7" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr"/>
+      <c r="N2" s="7" t="inlineStr"/>
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>https://quranenc.com/ar/browse/arabic_seraj/2</t>
         </is>
@@ -823,31 +843,42 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
+          <t>أي: إنَّ ما هم عليه من الشِّرك بالله تعالى والكفر به، أمرٌ أعظمُ من إزهاق نفوسهم، كما أنَّ محاولاتهم لصدِّ المؤمنين عن دِينهم؛ ليصيروا مِثلهم من المشركين، أشدُّ مِن أنْ يُقتلوا وهم مستمسِكون بدِينهم</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>تفسير الآيات</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr"/>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>https://dorar.net/tafseer/2/33</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
           <t>وَالْفِتْنَةُ: أَذًى لِلْمُسْلِمِينَ، أَوْ شِرْكٌ بِاللَّهِ.</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
         <is>
           <t>النزاع، أو الافتراء (كما شاع في الإندونيسية)</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr"/>
-      <c r="I3" s="8" t="inlineStr">
-        <is>
-          <t>متوسطة: الحروف متسقة، والحركات تحتاج مطابقة بالعين</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K3" s="7" t="inlineStr">
+      <c r="M3" s="7" t="inlineStr"/>
+      <c r="N3" s="7" t="inlineStr">
         <is>
           <t>للفظ معنيان في المصدر؛ تُقبل الإجابة بأيٍّ منهما. وهو مثال التوسع اللغوي</t>
         </is>
       </c>
-      <c r="L3" s="7" t="inlineStr">
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t>https://quranenc.com/ar/browse/arabic_seraj/2</t>
         </is>
@@ -859,7 +890,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>التَّهْلُكَة</t>
+          <t>يَشْرِي</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -871,35 +902,42 @@
         <v>2</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>التَّهْلُكَة: الهَلَاكُ بِتَرْكِ الجِهَادِ، وَالإِنْفَاقِ فِيهِ.</t>
+          <t>يَشْرِي: يَبِيع</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>الخطر عموماً</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr"/>
-      <c r="I4" s="8" t="inlineStr">
-        <is>
-          <t>متوسطة: الحروف متسقة، والحركات تحتاج مطابقة بالعين</t>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>https://dorar.net/tafseer/2/35</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
+          <t>يَشْرِي: يَبِيعُ.</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>فرق دقيق: المصدر يربطها بترك الجهاد والإنفاق</t>
+          <t>يوافقه</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>يشتري</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr"/>
+      <c r="N4" s="7" t="inlineStr"/>
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t>https://quranenc.com/ar/browse/arabic_seraj/2</t>
         </is>
@@ -911,45 +949,56 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>يَشْرِي</t>
+          <t>تَحُسُّونَهُمْ</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>البقرة</t>
+          <t>آل عمران</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>يَشْرِي: يَبِيعُ.</t>
+          <t>تَحُسُّونَهُمْ: أي: تَستأصِلونهم قتلًا، أو تقتلونهم، وأصْل حَسَس: غلبةُ الشَّيء بقتْل أو غيره، وحِكايةُ صوت عند توجُّعٍ وشَبَهِه</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>يشتري</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>متوسطة: الحروف متسقة، والحركات تحتاج مطابقة بالعين</t>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>https://dorar.net/tafseer/3/45</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="inlineStr"/>
+          <t>تَحُسُّونَهُم: تَقْتُلُونَهُم.</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/2</t>
+          <t>من الإحساس</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr"/>
+      <c r="N5" s="7" t="inlineStr"/>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/3</t>
         </is>
       </c>
     </row>
@@ -959,45 +1008,56 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>تَحُسُّونَهُم</t>
+          <t>مُرَاغَمًا</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>آل عمران</t>
+          <t>النساء</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>152</v>
+        <v>100</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>تَحُسُّونَهُم: تَقْتُلُونَهُم.</t>
+          <t>مُرَاغَمًا: أي: مُتَزَحْزَحًا عمَّا يَكرَهُه، أو مُتَحوَّلًا، والمُراغَم والمُهاجَر واحدٌ، وأصل (رغم): المَذهبُ والمهرَبُ</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>من الإحساس</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>متوسطة: الحروف متسقة، والحركات تحتاج مطابقة بالعين</t>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>https://dorar.net/tafseer/4/28</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr"/>
+          <t>مُرَاغَمًا: مُهَاجِرًا، وَمَكَانًا يَتَحَوَّلُ إِلَيْهِ.</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/3</t>
+          <t>من الإرغام والإكراه</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr"/>
+      <c r="N6" s="7" t="inlineStr"/>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/4</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1067,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>مُرَاغَمًا</t>
+          <t>يَفْتِنَكُمُ</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -1019,31 +1079,42 @@
         <v>4</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>مُرَاغَمًا: مُهَاجِرًا، وَمَكَانًا يَتَحَوَّلُ إِلَيْهِ.</t>
+          <t>يَفْتِنَكُمُ: أي: يَقْتُلَكمْ أو يَأسِرَكُم، وتُطلَق الفِتْنةُ كذلك على: الشِّرْك والكُفر، والشَّرِّ والعذاب، وهي في الأصل: الاختِبارُ والابتلاء والامتِحان، مأخوذةٌ من الفَتْن: وهو إدخالُ الذَّهبِ النَّارَ؛ لتظهَرَ جَودتُه من رداءتِه</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>من الإرغام والإكراه</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t>متوسطة: الحروف متسقة، والحركات تحتاج مطابقة بالعين</t>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>https://dorar.net/tafseer/4/29</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="inlineStr"/>
+          <t>يَفْتِنَكُمُ: يَعْتَدِي عَلَيْكُمْ.</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه في أصل المعنى</t>
+        </is>
+      </c>
       <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>أن يضلوكم عن دينكم</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr"/>
+      <c r="N7" s="7" t="inlineStr"/>
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t>https://quranenc.com/ar/browse/arabic_seraj/4</t>
         </is>
@@ -1055,45 +1126,60 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>يَفْتِنَكُمُ</t>
+          <t>عَلَى فَتْرَةٍ</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>النساء</t>
+          <t>المائدة</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>يَفْتِنَكُمُ: يَعْتَدِي عَلَيْكُمْ.</t>
+          <t>عَلَى فَتْرَةٍ: على حِين فُتورٍ من الإرسالِ، وانقطاعِ الوَحْيِ، وأصل الفُتور: السكون بعد الحِدَّة، واللِّينُ بعدَ الشِّدَّة، والضَّعْف بعد القُوَّة</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>أن يضلوكم عن دينكم</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr"/>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>متوسطة: الحروف متسقة، والحركات تحتاج مطابقة بالعين</t>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>https://dorar.net/tafseer/5/8</t>
         </is>
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr"/>
+          <t>فَتْرَةٍ: فُتُورٍ وَانْقِطَاعٍ، وَهِيَ المُدَّةُ بَيْنَ النَّبِيِّ عِيسَى وَنَبِيِّنَا مُحَمَّدٍ - عَلَيْهِمَا الصَّلَاةُ وَالسَّلَامُ -.</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/4</t>
+          <t>خلال مدة زمنية</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr"/>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>فرق دقيق: المصدر يجمع بين معنى الانقطاع والمدة</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/5</t>
         </is>
       </c>
     </row>
@@ -1103,49 +1189,56 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>فَتْرَةٍ</t>
+          <t>وَفَرْشًا</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>المائدة</t>
+          <t>الأنعام</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>19</v>
+        <v>142</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>فَتْرَةٍ: فُتُورٍ وَانْقِطَاعٍ، وَهِيَ المُدَّةُ بَيْنَ النَّبِيِّ عِيسَى وَنَبِيِّنَا مُحَمَّدٍ - عَلَيْهِمَا الصَّلَاةُ وَالسَّلَامُ -.</t>
+          <t>وَفَرْشًا: الفَرْشُ: صِغارُ الإبلِ التي لم تُدرِكْ أن يُحمَلَ عليها، وأصلُ (فرش): يَدُلُّ على تَمهيدِ الشَّيءِ، وبَسْطِه</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>خلال مدة زمنية</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr"/>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>عالية للحروف؛ تنوين «فتور» يحتاج مطابقة</t>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>https://dorar.net/tafseer/6/36</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
+          <t>وَفَرْشًا: مَا هُوَ مُهَيّأٌ لِغَيْرِ الْحَمْلِ لِصِغَرِهِ، وَقُرْبِهِ مِنَ الأَرضِ؛ كَالْغَنَمِ.</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>فرق دقيق: المصدر يجمع بين معنى الانقطاع والمدة</t>
+          <t>يوافقه في أصل المعنى</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/5</t>
+          <t>من الفراش</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr"/>
+      <c r="N9" s="7" t="inlineStr"/>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/6</t>
         </is>
       </c>
     </row>
@@ -1155,45 +1248,56 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>وَفَرْشًا</t>
+          <t>قَائِلُونَ</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>الأنعام</t>
+          <t>الأعراف</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>142</v>
+        <v>4</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>وَفَرْشًا: مَا هُوَ مُهَيّأٌ لِغَيْرِ الْحَمْلِ لِصِغَرِهِ، وَقُرْبِهِ مِنَ الأَرضِ؛ كَالْغَنَمِ.</t>
+          <t>قَائِلُونَ: أي: نائِمون نِصفَ النَّهَارِ في وَقْتِ القائِلَةِ</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>من الفراش</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/7/2</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="inlineStr"/>
+          <t>قَائِلُونَ: نَائِمُونَ فِي نِصْفِ النَّهَارِ.</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/6</t>
+          <t>من القول والكلام</t>
+        </is>
+      </c>
+      <c r="M10" s="7" t="inlineStr"/>
+      <c r="N10" s="7" t="inlineStr"/>
+      <c r="O10" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/7</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1307,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>قَائِلُونَ</t>
+          <t>أَقَلَّتْ</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -1215,31 +1319,42 @@
         <v>7</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>قَائِلُونَ: نَائِمُونَ فِي نِصْفِ النَّهَارِ.</t>
+          <t>أَقَلَّتْ: أي: حمَلَتْ؛ يُقال: أقلَ فلَانٌ الشَّيْءَ واستقلَّ به: إذا أطاقَه وحمَلَه، وأقْلَلْت كذا: وجدتَه قليلَ المحمَلِ أي: خفيفًا، وأصلُ (قلل): يدلُّ على نَزارةِ الشَّيءِ، وعلى الانزعاجِ الذي هو خِلافُ الاستقرارِ</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>من القول والكلام</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr"/>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/7/14</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="inlineStr"/>
+          <t>أَقَلَّتْ: حَمَلَتْ.</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>قلّلت</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr"/>
+      <c r="N11" s="7" t="inlineStr"/>
+      <c r="O11" s="7" t="inlineStr">
         <is>
           <t>https://quranenc.com/ar/browse/arabic_seraj/7</t>
         </is>
@@ -1251,7 +1366,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>أَقَلَّتْ</t>
+          <t>عَفَوْا</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -1263,31 +1378,42 @@
         <v>7</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>أَقَلَّتْ: حَمَلَتْ.</t>
+          <t>عَفَوْا: أي: كَثُروا، وزَادوا، وأَصْلُ العَفْوِ: تَرْكُ الشَّيءِ</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>قلّلت</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr"/>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/7/21</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="inlineStr"/>
+          <t>عَفَوْا: كَثُرُوا وَنَمَوْا عَدَدًا وَمَالًا.</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>من العفو والمسامحة</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="inlineStr"/>
+      <c r="N12" s="7" t="inlineStr"/>
+      <c r="O12" s="7" t="inlineStr">
         <is>
           <t>https://quranenc.com/ar/browse/arabic_seraj/7</t>
         </is>
@@ -1299,7 +1425,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>عَفَوْا</t>
+          <t>بِالسِّنِينَ</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -1311,31 +1437,42 @@
         <v>7</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>عَفَوْا: كَثُرُوا وَنَمَوْا عَدَدًا وَمَالًا.</t>
+          <t>بِالسِّنِينَ: جَمْعُ سَنَةٍ، وهي: الجَدْبُ والقَحْطُ؛ وأكثرُ ما تُستعمَلُ السَّنَةُ في الحولِ الذي فيه الجدبُ، يُقالُ: أسْنَتَ القَومُ: إذا أَجْدَبوا، وأَصْلُ (سنه): يَدُلُّ على زَمانٍ</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>من العفو والمسامحة</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/7/27</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr"/>
+          <t>بِالسِّنِينَ: بِالْقَحْطِ، وَالْجَدْبِ.</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>بالأعوام</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr"/>
+      <c r="N13" s="7" t="inlineStr"/>
+      <c r="O13" s="7" t="inlineStr">
         <is>
           <t>https://quranenc.com/ar/browse/arabic_seraj/7</t>
         </is>
@@ -1347,7 +1484,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>بِالسِّنِينَ</t>
+          <t>تَحْمِلْ عَلَيْهِ</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -1359,31 +1496,42 @@
         <v>7</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>بِالسِّنِينَ: بِالْقَحْطِ، وَالْجَدْبِ.</t>
+          <t>تَحْمِلْ عَلَيْهِ: أي: تَزجُرْه، أو تَطرُدْه، وأَصلُ (حمل): يَدُلُّ عَلَى إِقْلَالِ الشَّيْءِ، يُقَالُ: حَمَلْتُ الشَّيْءَ أَحْمِلُه حَمْلًا</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>بالأعوام</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr"/>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/7/42</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="inlineStr"/>
+          <t>تَحْمِلْ عَلَيْهِ: تَطْرُدْهُ.</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>تُحمّله الأثقال</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="inlineStr"/>
+      <c r="N14" s="7" t="inlineStr"/>
+      <c r="O14" s="7" t="inlineStr">
         <is>
           <t>https://quranenc.com/ar/browse/arabic_seraj/7</t>
         </is>
@@ -1395,45 +1543,56 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>تَحْمِلْ عَلَيْهِ</t>
+          <t>جَارٌ لَكُمْ</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>الأعراف</t>
+          <t>الأنفال</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>176</v>
+        <v>48</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>تَحْمِلْ عَلَيْهِ: تَطْرُدْهُ.</t>
+          <t>جَارٌ لَكُمْ: أي: مُجِيرٌ لكم، ومانعُكم منهم</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>تُحمّله الأثقال</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr"/>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/8/16</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="inlineStr"/>
+          <t>جَارٌ لَّكُمْ: نَاصِرُكُمْ، وَمُجِيرُكُمْ.</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه في أصل المعنى</t>
+        </is>
+      </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/7</t>
+          <t>الجار الساكن بجوارهم</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr"/>
+      <c r="N15" s="7" t="inlineStr"/>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/8</t>
         </is>
       </c>
     </row>
@@ -1443,45 +1602,56 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>جَارٌ لَّكُمْ</t>
+          <t>مُرْجَوْنَ</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>الأنفال</t>
+          <t>التوبة</t>
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>جَارٌ لَّكُمْ: نَاصِرُكُمْ، وَمُجِيرُكُمْ.</t>
+          <t>مُرْجَوْنَ: أي: مُؤَخَّرونَ، وأصلُ (رجأ): يدلُّ على التَّأخيرِ</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>الجار الساكن بجوارهم</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr"/>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/9/39</t>
         </is>
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="inlineStr"/>
+          <t>مُرْجَوْنَ: مُؤَخَّرُونَ.</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/8</t>
+          <t>من الرجاء</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr"/>
+      <c r="N16" s="7" t="inlineStr"/>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/9</t>
         </is>
       </c>
     </row>
@@ -1491,45 +1661,64 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>مُرْجَوْنَ</t>
+          <t>سَيَّارَةٌ</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>التوبة</t>
+          <t>يوسف</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>106</v>
+        <v>19</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>مُرْجَوْنَ: مُؤَخَّرُونَ.</t>
+          <t>السَّيَّارَةِ: أي: مارَّةِ الطَّريقِ مِن المُسافرينَ، وأصلُ (سير): يدُلُّ على مُضيٍّ وجَرَيانٍ</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>من الرجاء</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr"/>
+          <t>غريب الكلمات</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>يوسف 10</t>
+        </is>
+      </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/12/3</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="inlineStr"/>
+          <t>سَيَّارَةٌ: جَمَاعَةٌ مِنَ المُسَافِرِينَ.</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/9</t>
+          <t>المركبة</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr"/>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>شرحته الموسوعة عند أول ورود للكلمة (يوسف 10)، ويشرحها «السراج» في الموضعين</t>
+        </is>
+      </c>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/12</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1728,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>سَيَّارَةٌ</t>
+          <t>وَقَطَّعْنَ</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1551,35 +1740,42 @@
         <v>12</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>سَيَّارَةٌ: جَمَاعَةٌ مِنَ المُسَافِرِينَ.</t>
+          <t>أي: وجَرَحنَ أيديَهنَّ بالسَّكاكينِ، وهُنَّ يَحسَبنَ أنَّهنَّ يُقَطِّعنَ الطَّعامَ؛ لدَهشتِهنَّ بما رأينَ مِن جمالِ يوسُفَ</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>المركبة</t>
+          <t>تفسير الآيات</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr"/>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/12/8</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>مثال معروف (المعنى المعاصر للكلمة)</t>
+          <t>وَقَطَّعْنَ: جَرَحْنَ.</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>ويشرحها المصدر أيضاً في 12:10</t>
+          <t>يوافقه</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>بترن أيديهن</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr"/>
+      <c r="N18" s="7" t="inlineStr"/>
+      <c r="O18" s="7" t="inlineStr">
         <is>
           <t>https://quranenc.com/ar/browse/arabic_seraj/12</t>
         </is>
@@ -1591,7 +1787,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>وَقَطَّعْنَ</t>
+          <t>مَا نَبْغِي</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1603,31 +1799,42 @@
         <v>12</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>وَقَطَّعْنَ: جَرَحْنَ.</t>
+          <t>مَا نَبْغِي: أيْ: أيَّ شيءٍ نطلُبُ وراءَ هذا، أو ماذا نريدُ؟ وأصْلُ (بغي): يدل على طلَبِ الشَّيءِ</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>بترن أيديهن</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr"/>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/12/14</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="inlineStr"/>
+          <t>مَا نَبْغِي: مَاذَا نَطْلُبُ أَكْثَرَ مِنْ هَذَا؟</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>من البغي والعدوان</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr"/>
+      <c r="N19" s="7" t="inlineStr"/>
+      <c r="O19" s="7" t="inlineStr">
         <is>
           <t>https://quranenc.com/ar/browse/arabic_seraj/12</t>
         </is>
@@ -1639,45 +1846,56 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>مَا نَبْغِي</t>
+          <t>بِمُصْرِخِكُمْ</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>يوسف</t>
+          <t>إبراهيم</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>مَا نَبْغِي: مَاذَا نَطْلُبُ أَكْثَرَ مِنْ هَذَا؟</t>
+          <t>بِمُصْرِخِكُمْ: أي: بمُغيثِكم ومُنقِذِكم، وأصلُ (صرخ): يدلُّ على صَوتٍ رَفيعٍ</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>من البغي والعدوان</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr"/>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/14/6</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="inlineStr"/>
+          <t>بِمُصْرِخِكُمْ: بِمُغِيثكُمْ.</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/12</t>
+          <t>من الصراخ</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr"/>
+      <c r="N20" s="7" t="inlineStr"/>
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/14</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1905,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>بِمُصْرِخِكُمْ</t>
+          <t>مُقْنِعِي رُءُوسِهِمْ</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1699,31 +1917,42 @@
         <v>14</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>بِمُصْرِخِكُمْ: بِمُغِيثكُمْ.</t>
+          <t>مُقْنِعِي رُءُوسِهِمْ: أي: رافِعِيها مع الإقبالِ بأبصارِهم إلى ما بينَ أيديهم، مِن غيرِ التفاتٍ إلى شَيءٍ، وأصلُ (قنع): ارتفاعُ الشَّيءِ ليس فيه تَصَوُّبٌ، وأيضًا يدُلُّ على الإقبالِ على الشَّيءِ</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>من الصراخ</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr"/>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/14/11</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="inlineStr"/>
+          <t>مُقْنِعِي رُؤُوسِهِمْ: رَافِعِي رُؤُوسِهِمْ.</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه في أصل المعنى</t>
+        </is>
+      </c>
       <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>من الإقناع، أو مغطّين رؤوسهم بالقناع</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr"/>
+      <c r="N21" s="7" t="inlineStr"/>
+      <c r="O21" s="7" t="inlineStr">
         <is>
           <t>https://quranenc.com/ar/browse/arabic_seraj/14</t>
         </is>
@@ -1735,45 +1964,56 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>مُقْنِعِي رُؤُوسِهِمْ</t>
+          <t>كِتَابٌ مَّعْلُومٌ</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>إبراهيم</t>
+          <t>الحجر</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>مُقْنِعِي رُؤُوسِهِمْ: رَافِعِي رُؤُوسِهِمْ.</t>
+          <t>أي: وما أهلَكْنا أهلَ قريةٍ يستَحِقُّونَ العذابَ إلَّا وكان لهلاكِهم زمنٌ محدَّدٌ مكتوبٌ في اللَّوحِ المحفوظِ، فلا نُهلِكُهم حتى يَبلُغوه</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>من الإقناع، أو مغطّين رؤوسهم بالقناع</t>
+          <t>تفسير الآيات</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr"/>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/15/1</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="inlineStr"/>
+          <t>كِتَابٌ مَّعْلُومٌ: أَجَلٌ مُقَدَّرٌ.</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/14</t>
+          <t>كتاب مقروء معروف</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr"/>
+      <c r="N22" s="7" t="inlineStr"/>
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/15</t>
         </is>
       </c>
     </row>
@@ -1783,45 +2023,56 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>كِتَابٌ مَّعْلُومٌ</t>
+          <t>طَائِرَهُ</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>الحجر</t>
+          <t>الإسراء</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>كِتَابٌ مَّعْلُومٌ: أَجَلٌ مُقَدَّرٌ.</t>
+          <t>طَائِرَهُ: أي: عَمَلَه مِن خَيرٍ أو شَرٍّ، وما قُدِّرَ عليه، تقولُ العربُ: جرَى طائرُه بكذا مِن الخيرِ، وجرَى له الطائرُ بكذا مِن الشَّرِّ، فخُوطبوا بما يَستعمِلونَ، والطائرُ: الحظُّ</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>كتاب مقروء معروف</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr"/>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/17/4</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="inlineStr"/>
+          <t>طَائِرَهُ: مَا عَمِلَهُ مِنْ خَيْرٍ وَشَرٍّ.</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/15</t>
+          <t>الطير</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="inlineStr"/>
+      <c r="N23" s="7" t="inlineStr"/>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/17</t>
         </is>
       </c>
     </row>
@@ -1831,45 +2082,64 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>سُكِّرَتْ</t>
+          <t>مُبْصِرَةً</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>الحجر</t>
+          <t>الإسراء</t>
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>سُكِّرَتْ: سُحِرَتْ.</t>
+          <t>مُبْصِرَةً: أي: بَيِّنةً، واضِحةَ الدَّلالةِ، وأصلُ البصَرِ: العِلمُ بالشَّيءِ</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>من السُّكر، أو بمعنى أُغلقت</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr"/>
+          <t>غريب الكلمات</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>النمل 13</t>
+        </is>
+      </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/27/2</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K24" s="7" t="inlineStr"/>
+          <t>مُبْصِرَةً: مُعْجِزَةً وَاضِحَةً.</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/15</t>
+          <t>ناقة ترى وتبصر</t>
+        </is>
+      </c>
+      <c r="M24" s="7" t="inlineStr"/>
+      <c r="N24" s="7" t="inlineStr">
+        <is>
+          <t>شرحته الموسوعة في «غريب الكلمات» عند النمل 13 بالمعنى نفسه</t>
+        </is>
+      </c>
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/17</t>
         </is>
       </c>
     </row>
@@ -1879,7 +2149,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>طَائِرَهُ</t>
+          <t>ضِعْفَ الْحَيَاةِ</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1891,31 +2161,46 @@
         <v>17</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>طَائِرَهُ: مَا عَمِلَهُ مِنْ خَيْرٍ وَشَرٍّ.</t>
+          <t>أي: لو رَكَنْتَ قليلًا إلى المُشرِكينَ -يا مُحَمَّدُ- ففَعَلْتَ بعضَ ما سألوك، لأذقْناك عَذابًا مُضاعَفًا في الحياةِ الدُّنيا وفي الآخِرةِ</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>الطير</t>
+          <t>تفسير الآيات</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/17/18</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="inlineStr"/>
+          <t>ضِعْفَ الْحَيَاةِ: عَذَابًا مُضَاعَفًا فِي الدُّنْيَا.</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>الضَّعف: ضد القوة</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="inlineStr"/>
+      <c r="N25" s="7" t="inlineStr">
+        <is>
+          <t>في المصدر سطر ثانٍ لـ«وضعف الممات»</t>
+        </is>
+      </c>
+      <c r="O25" s="7" t="inlineStr">
         <is>
           <t>https://quranenc.com/ar/browse/arabic_seraj/17</t>
         </is>
@@ -1927,45 +2212,56 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>مُبْصِرَةً</t>
+          <t>تَقْرِضُهُمْ</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>الإسراء</t>
+          <t>الكهف</t>
         </is>
       </c>
       <c r="D26" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E26" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E26" s="6" t="n">
-        <v>59</v>
-      </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>مُبْصِرَةً: مُعْجِزَةً وَاضِحَةً.</t>
+          <t>تَقْرِضُهُمْ: أي: تُجاوِزُهم وتَدَعُهم، أي: لا تَطلُعُ في كَهفِهم، يُقالُ: قرضْتُ موضعَ كذا؛ إذا قطعتَه فجاوزتَه، وأصلُ (قرض): يدلُّ على القَطعِ</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>ناقة ترى وتبصر</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr"/>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/18/5</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="inlineStr"/>
+          <t>تَّقْرِضُهُمْ: تَتْرُكُهُمْ، وَتَتَجَاوَزُ عَنْهُمْ.</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/17</t>
+          <t>من القرض أو القرص</t>
+        </is>
+      </c>
+      <c r="M26" s="7" t="inlineStr"/>
+      <c r="N26" s="7" t="inlineStr"/>
+      <c r="O26" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/18</t>
         </is>
       </c>
     </row>
@@ -1975,49 +2271,60 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>ضِعْفَ الْحَيَاةِ</t>
+          <t>فَأَجَاءَهَا</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>الإسراء</t>
+          <t>مريم</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>ضِعْفَ الْحَيَاةِ: عَذَابًا مُضَاعَفًا فِي الدُّنْيَا.</t>
+          <t>فَأَجَاءَهَا: أي: ألجَأها واضْطرَّها، يُقالُ: جاء بها وأجاءَها: بمعنًى</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>الضَّعف: ضد القوة</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr"/>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/19/5</t>
         </is>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
+          <t>فَأَجَاءَهَا: فَأَلْجَأَهَا طَلْقُ الحَمْلِ.</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>في المصدر سطر ثانٍ لـ«وضعف الممات»</t>
+          <t>يوافقه</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/17</t>
+          <t>فجاءها المخاض</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr"/>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>فرق دقيق: الموسوعة تقول «جاء بها وأجاءها: بمعنًى»، أي جاء بها لا جاءها</t>
+        </is>
+      </c>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/19</t>
         </is>
       </c>
     </row>
@@ -2027,45 +2334,56 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>نَافِلَةً لَّكَ</t>
+          <t>وَأَهُشُّ</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>الإسراء</t>
+          <t>طه</t>
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>79</v>
+        <v>18</v>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>نَافِلَةً لَّكَ: زِيَادَةً لَكَ فِي عُلُوِّ القَدْرِ، وَرَفْعِ الدَّرَجَاتِ.</t>
+          <t>وَأَهُشُّ: أي: أضرِبُ بها الشَّجرَ؛ لِيَسقُطَ وَرَقُه فترعاه الغَنَمُ، والهَشُّ: يقارِبُ الهزَّ في التَّحريكِ</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>صلاة سنة غير واجبة</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr"/>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/20/3</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="inlineStr"/>
+          <t>وَأَهُشُّ بِهَا عَلَى غَنَمِي: أَهُزُّ بِهَا الشَّجَرَ؛ لِتَرْعَى غَنَمِي مَا يَتَسَاقَطُ مِنْ وَرَقِهِ.</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/17</t>
+          <t>أطرد بها وأزجر</t>
+        </is>
+      </c>
+      <c r="M28" s="7" t="inlineStr"/>
+      <c r="N28" s="7" t="inlineStr"/>
+      <c r="O28" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/20</t>
         </is>
       </c>
     </row>
@@ -2075,45 +2393,56 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>تَّقْرِضُهُمْ</t>
+          <t>مِّنْ أَثَرِ الرَّسُولِ</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>الكهف</t>
+          <t>طه</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>تَّقْرِضُهُمْ: تَتْرُكُهُمْ، وَتَتَجَاوَزُ عَنْهُمْ.</t>
+          <t>أي: فأخذتُ بكَفِّي ترابًا من أثَرِ حافِرِ فَرَسِ جِبريلَ</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>من القرض أو القرص</t>
+          <t>تفسير الآيات</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr"/>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/20/13</t>
         </is>
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="inlineStr"/>
+          <t>مِّنْ أَثَرِ الرَّسُولِ: مِنْ أَثَرِ حَافِرِ فَرَسِ جِبْرِيلَ - عليه السلام -.</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/18</t>
+          <t>أثر النبي موسى عليه السلام</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr"/>
+      <c r="N29" s="7" t="inlineStr"/>
+      <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/20</t>
         </is>
       </c>
     </row>
@@ -2123,49 +2452,56 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>فَأَجَاءَهَا</t>
+          <t>نَقْدِرَ عَلَيْهِ</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>مريم</t>
+          <t>الأنبياء</t>
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>فَأَجَاءَهَا: فَأَلْجَأَهَا طَلْقُ الحَمْلِ.</t>
+          <t>نَقْدِرَ عَلَيْهِ: أي: نُضَيِّقَ عليه، مِن قَولِهم: قَدَرْتُ على فُلانٍ: إذا ضَيَّقْتَ عليه، وقيل: نَقْدِرُ: بمعنى نُقَدِّرُ، والمعنى لن نُقَدِّرَ عليه ما قَدَّرْنا مِن كَونِه في بطنِ الحوتِ</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>فجاءها المخاض</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr"/>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/21/17</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
+          <t>أَن لَّن نَّقْدِرَ عَلَيْهِ: أَن لَّنْ نُضَيِّقَ عَلَيْهِ فِي بَطْنِ الحُوتِ، وَنُؤَاخِذَهُ.</t>
         </is>
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>المصدر يشرح «فأجاءها» و«المخاض» في سطرين</t>
+          <t>يوافقه</t>
         </is>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/19</t>
+          <t>لن نستطيع عليه</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr"/>
+      <c r="N30" s="7" t="inlineStr"/>
+      <c r="O30" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/21</t>
         </is>
       </c>
     </row>
@@ -2175,45 +2511,56 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>وَأَهُشُّ بِهَا عَلَى غَنَمِي</t>
+          <t>السِّجِلِّ</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>طه</t>
+          <t>الأنبياء</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>وَأَهُشُّ بِهَا عَلَى غَنَمِي: أَهُزُّ بِهَا الشَّجَرَ؛ لِتَرْعَى غَنَمِي مَا يَتَسَاقَطُ مِنْ وَرَقِهِ.</t>
+          <t>السِّجِلِّ: أي: الصَّحيفةِ التي فيها الكِتابُ، يعني: المكتوبَ، والسِّجِلُ: اسمٌ مُشتَقٌّ مِن المُساجَلةِ، وهي: المُكاتَبةُ</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>أطرد بها وأزجر</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr"/>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/21/21</t>
         </is>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="inlineStr"/>
+          <t>كَطَيِّ السِّجِلِّ لِلْكُتُبِ: كَمَا تُطْوَى الصَّحِيفَةُ عَلَى مَا كُتِبَ فِيهَا.</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/20</t>
+          <t>السجلّ: الدفتر الرسمي، والكتب: المؤلفات</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="inlineStr"/>
+      <c r="N31" s="7" t="inlineStr"/>
+      <c r="O31" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/21</t>
         </is>
       </c>
     </row>
@@ -2223,45 +2570,56 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>مِّنْ أَثَرِ الرَّسُولِ</t>
+          <t>رِجَالًا</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>طه</t>
+          <t>الحج</t>
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>مِّنْ أَثَرِ الرَّسُولِ: مِنْ أَثَرِ حَافِرِ فَرَسِ جِبْرِيلَ - عليه السلام -.</t>
+          <t>رِجَالًا: جمعُ راجِلٍ، أي: مُشاةً، يُقالُ للماشي بالرِّجْل: رَجِلٌ وراجِلٌ، وهو مشتقٌّ من الرِّجْلِ</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>أثر النبي موسى عليه السلام</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr"/>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/22/10</t>
         </is>
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="inlineStr"/>
+          <t>رِجَالًا: يَمْشُونَ عَلَى أَقْدَامِهِمْ؛ جَمْعُ رَاجِلٍ.</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/20</t>
+          <t>الذكور من الناس</t>
+        </is>
+      </c>
+      <c r="M32" s="7" t="inlineStr"/>
+      <c r="N32" s="7" t="inlineStr"/>
+      <c r="O32" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/22</t>
         </is>
       </c>
     </row>
@@ -2271,45 +2629,56 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>أَن لَّن نَّقْدِرَ عَلَيْهِ</t>
+          <t>كَمِشْكَاةٍ</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>الأنبياء</t>
+          <t>النور</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>أَن لَّن نَّقْدِرَ عَلَيْهِ: أَن لَّنْ نُضَيِّقَ عَلَيْهِ فِي بَطْنِ الحُوتِ، وَنُؤَاخِذَهُ.</t>
+          <t>كَمِشْكَاةٍ: المشكاةُ: الكَوَّةُ فِي الحائِطِ غيرُ النافذةِ يُوضَعُ فيها المصباحُ، وقيل: مَوضِعُ الفتيلةِ مِن القنديلِ، واختُلِف هل هي عربيةٌ أو حبشيَّةٌ مُعَرَّبةٌ</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>لن نستطيع عليه</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr"/>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/24/10</t>
         </is>
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K33" s="7" t="inlineStr"/>
+          <t>كَمِشْكَاةٍ: هِيَ: الكُوَّةُ فِي الحَائِطِ غَيْرُ النَّافِذَةِ.</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/21</t>
+          <t>المصباح نفسه</t>
+        </is>
+      </c>
+      <c r="M33" s="7" t="inlineStr"/>
+      <c r="N33" s="7" t="inlineStr"/>
+      <c r="O33" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/24</t>
         </is>
       </c>
     </row>
@@ -2319,45 +2688,60 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>كَطَيِّ السِّجِلِّ لِلْكُتُبِ</t>
+          <t>الْمَاءِ</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>الأنبياء</t>
+          <t>الفرقان</t>
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>كَطَيِّ السِّجِلِّ لِلْكُتُبِ: كَمَا تُطْوَى الصَّحِيفَةُ عَلَى مَا كُتِبَ فِيهَا.</t>
+          <t>وهو وحْدَه الذي خلَقَ مِن المَنيِّ إنسانًا، فجعَلَ ذلك الإنسانَ ذا نَسَبٍ وذا صِهرٍ، ولم يزَلْ سُبحانَه قَديرًا على كلِّ شَيءٍ</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>السجلّ: الدفتر الرسمي، والكتب: المؤلفات</t>
+          <t>المعنى الإجمالي</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr"/>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/25/11</t>
         </is>
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="inlineStr"/>
+          <t>الْمَاءِ: مَنِيِّ الرَّجُلِ وَالمَرْأَةِ.</t>
+        </is>
+      </c>
+      <c r="K34" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/21</t>
+          <t>الماء المعروف الذي نشربه</t>
+        </is>
+      </c>
+      <c r="M34" s="7" t="inlineStr"/>
+      <c r="N34" s="7" t="inlineStr">
+        <is>
+          <t>من «المعنى الإجمالي»</t>
+        </is>
+      </c>
+      <c r="O34" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/25</t>
         </is>
       </c>
     </row>
@@ -2367,45 +2751,56 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>رِجَالًا</t>
+          <t>الْحَيَوَانُ</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>الحج</t>
+          <t>العنكبوت</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>رِجَالًا: يَمْشُونَ عَلَى أَقْدَامِهِمْ؛ جَمْعُ رَاجِلٍ.</t>
+          <t>الْحَيَوَانُ: أي: الحياةُ الدَّائِمةُ الَّتي لا زوالَ لها، ولفظُ الحيوانِ مصدرٌ كالحياةِ، وأصلُ (حيي): يدُلُّ على خِلافِ الموتِ</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>الذكور من الناس</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr"/>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/29/18</t>
         </is>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="inlineStr"/>
+          <t>الْحَيَوَانُ: الحَيَاةُ الحَقِيقِيَّةُ الكَامِلَةُ الدَّائِمَةُ.</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/22</t>
+          <t>البهائم والدواب</t>
+        </is>
+      </c>
+      <c r="M35" s="7" t="inlineStr"/>
+      <c r="N35" s="7" t="inlineStr"/>
+      <c r="O35" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/29</t>
         </is>
       </c>
     </row>
@@ -2415,49 +2810,60 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>وَجِلَةٌ</t>
+          <t>مَرَحًا</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>المؤمنون</t>
+          <t>لقمان</t>
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>وَجِلَةٌ: خَائِفَةٌ مِنْ عَدَمِ القَبُولِ.</t>
+          <t>مَرَحًا: أي: اختيالًا وبطرًا وكبرًا وفخرًا، والمَرَحُ: شدَّةُ الفرحِ والتَّوسُّعُ فيه، وأصلُ (مرح): يدلُ على مَسَرَّةٍ لا يكادُ يستَقِرُّ معها المرءُ طَرَبًا</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>خائفة من ذنوبها</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr"/>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/31/6</t>
         </is>
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
+          <t>مَرَحًا: مُخْتَالًا مُتَبَخْتَرًا.</t>
         </is>
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>فرق دقيق: المعنى العام صحيح، والفرق في سبب الخوف؛ يناسب تصنيف «جزئي»</t>
+          <t>يوافقه في أصل المعنى</t>
         </is>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/23</t>
+          <t>الفرح والسرور</t>
+        </is>
+      </c>
+      <c r="M36" s="7" t="inlineStr"/>
+      <c r="N36" s="7" t="inlineStr">
+        <is>
+          <t>فرق دقيق: الموسوعة تذكر أن أصل المرح شدة الفرح، والمراد في الآية الاختيال والبطر</t>
+        </is>
+      </c>
+      <c r="O36" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/31</t>
         </is>
       </c>
     </row>
@@ -2467,45 +2873,60 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>كَمِشْكَاةٍ</t>
+          <t>وَاقْصِدْ</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>النور</t>
+          <t>لقمان</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>كَمِشْكَاةٍ: هِيَ: الكُوَّةُ فِي الحَائِطِ غَيْرُ النَّافِذَةِ.</t>
+          <t>وَاقْصِدْ: أي: تَواضَعْ واعتَدِلْ، وأصلُ القَصدِ: استِقامةُ الطَّريقِ</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>القنديل أو المصباح نفسه</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr"/>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/31/6</t>
         </is>
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="inlineStr"/>
+          <t>وَاقْصِدْ: تَوَاضَعْ، وَكُنْ بَيْنَ المُسْرِعِ، وَالمُبْطِئِ.</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه في أصل المعنى</t>
+        </is>
+      </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/24</t>
+          <t>انوِ وجهة مشيك</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="inlineStr"/>
+      <c r="N37" s="7" t="inlineStr">
+        <is>
+          <t>السطر المطلوب متطابق في كل النسخ؛ اختلفت النسخ في حركة سطر آخر من الآية</t>
+        </is>
+      </c>
+      <c r="O37" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/31</t>
         </is>
       </c>
     </row>
@@ -2515,45 +2936,56 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>الْمَاءِ</t>
+          <t>ضَلَلْنَا فِي الْأَرْضِ</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>الفرقان</t>
+          <t>السجدة</t>
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>الْمَاءِ: مَنِيِّ الرَّجُلِ وَالمَرْأَةِ.</t>
+          <t>أي: وقال المُشرِكونَ استِبعادًا للبَعثِ: أإذا ذَهَبَت في الأرضِ أجسادُنا، وتفَرَّقَت فيها لحومُنا وعِظامُنا، وغابت في التُّرابِ وصارت مِثلَه، دون أن يتميَّزَ بَعضُه مِن بَعضٍ: أنَعودُ أحياءً مِن بعدِ تلك الحالِ</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>الماء المعروف الذي نشربه</t>
+          <t>تفسير الآيات</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr"/>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/32/2</t>
         </is>
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="inlineStr"/>
+          <t>ضَلَلْنَا فِي الْأَرْضِ: تَحَوَّلْنَا تُرَابًا بَعْدَ المَوْتِ.</t>
+        </is>
+      </c>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/25</t>
+          <t>تُهنا وأضعنا الطريق</t>
+        </is>
+      </c>
+      <c r="M38" s="7" t="inlineStr"/>
+      <c r="N38" s="7" t="inlineStr"/>
+      <c r="O38" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/32</t>
         </is>
       </c>
     </row>
@@ -2563,45 +2995,56 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>الْحَيَوَانُ</t>
+          <t>مَكَانَتِكُمْ</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>العنكبوت</t>
+          <t>الزمر</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>الْحَيَوَانُ: الحَيَاةُ الحَقِيقِيَّةُ الكَامِلَةُ الدَّائِمَةُ.</t>
+          <t>مَكَانَتِكُمْ: أي: طَريقتِكم الَّتي أنتم عليها، تقولُ للرَّجُلِ إذا أمَرْتَه أن يَثبُتَ على حالِه: على مكانَتِك يا فُلانُ، أي: اثبُتْ على ما أنت عليه</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>البهائم والدواب</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr"/>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/39/11</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="inlineStr"/>
+          <t>مَكَانَتِكُمْ: حَالَتِكُمُ الَّتِي رَضِيتُمُوهَا لِأَنْفُسِكُمْ.</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/29</t>
+          <t>المنزلة والقدر</t>
+        </is>
+      </c>
+      <c r="M39" s="7" t="inlineStr"/>
+      <c r="N39" s="7" t="inlineStr"/>
+      <c r="O39" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/39</t>
         </is>
       </c>
     </row>
@@ -2611,45 +3054,56 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>مَرَحًا</t>
+          <t>يَصِدُّونَ</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>لقمان</t>
+          <t>الزخرف</t>
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>مَرَحًا: مُخْتَالًا مُتَبَخْتَرًا.</t>
+          <t>يَصِدُّونَ: أي: يَضِجُّونَ، وقيل: يَضْحَكون، يُقالُ: صَدَّ يَصِدُّ، وذلك إذا ضَجَّ</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>الفرح والسرور</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr"/>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/43/11</t>
         </is>
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="inlineStr"/>
+          <t>يَصِدُّونَ: يَضَجُّونَ، وَيَصِيحُونَ، فَرَحًا، وَجَذَلًا.</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/31</t>
+          <t>يُعرضون (من الصدود)</t>
+        </is>
+      </c>
+      <c r="M40" s="7" t="inlineStr"/>
+      <c r="N40" s="7" t="inlineStr"/>
+      <c r="O40" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/43</t>
         </is>
       </c>
     </row>
@@ -2659,49 +3113,56 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>وَاقْصِدْ</t>
+          <t>شِرْكٌ</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>لقمان</t>
+          <t>الأحقاف</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>وَاقْصِدْ: تَوَاضَعْ، وَكُنْ بَيْنَ المُسْرِعِ، وَالمُبْطِئِ.</t>
+          <t>شِرْكٌ: أي: نَصيبٌ وشَرِكةٌ، وأصلُ (شرك): يدُلُّ على مُقارَنةٍ</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>انوِ وجهة مشيك</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr"/>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/46/2</t>
         </is>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
+          <t>لَهُمْ شِرْكٌ: شِرْكَةٌ وَنَصِيبٌ مَعَ اللهِ تَعَالَى فِي خَلْقِ السَّمَوَاتِ.</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>السطر المطلوب متطابق في كل النسخ؛ اختلفت النسخ في حركة سطر آخر من الآية</t>
+          <t>يوافقه</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/31</t>
+          <t>الشرك بالله</t>
+        </is>
+      </c>
+      <c r="M41" s="7" t="inlineStr"/>
+      <c r="N41" s="7" t="inlineStr"/>
+      <c r="O41" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/46</t>
         </is>
       </c>
     </row>
@@ -2711,45 +3172,56 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>ضَلَلْنَا فِي الْأَرْضِ</t>
+          <t>فَنَقَّبُوا</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>السجدة</t>
+          <t>ق</t>
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>ضَلَلْنَا فِي الْأَرْضِ: تَحَوَّلْنَا تُرَابًا بَعْدَ المَوْتِ.</t>
+          <t>فَنَقَّبُوا: أي: طافوا وسارُوا وتوَغَّلوا، وأصلُه مِنَ النَّقْبِ: وهو الطَّريقُ، كأنَّهم سَلَكوا كُلَّ طَريقٍ، أو مِن التَّنقُّبِ عن الأمرِ، بمعنى البحثِ عنه، وأصلُ (نقب): يدُلُّ على فَتحِ شَيءٍ</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>تُهنا وأضعنا الطريق</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr"/>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/50/7</t>
         </is>
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="inlineStr"/>
+          <t>فَنَقَّبُوا: طَوَّفُوا.</t>
+        </is>
+      </c>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/32</t>
+          <t>حفروا في الأرض (من التنقيب)</t>
+        </is>
+      </c>
+      <c r="M42" s="7" t="inlineStr"/>
+      <c r="N42" s="7" t="inlineStr"/>
+      <c r="O42" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/50</t>
         </is>
       </c>
     </row>
@@ -2759,45 +3231,56 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>مَكَانَتِكُمْ</t>
+          <t>صَرَّةٍ</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>الزمر</t>
+          <t>الذاريات</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>مَكَانَتِكُمْ: حَالَتِكُمُ الَّتِي رَضِيتُمُوهَا لِأَنْفُسِكُمْ.</t>
+          <t>صَرَّةٍ: أي: ضَجَّةٍ، وشِدَّةِ صِياحٍ، ومنه أُخِذَ صَريرُ البابِ، وهو صوتُه، وأصلُ (صرر): يدُلُّ على صَوتٍ</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>المنزلة والقدر</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr"/>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/51/5</t>
         </is>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="inlineStr"/>
+          <t>صَرَّةٍ: صَيْحَةٍ، وَضَجَّةٍ.</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/39</t>
+          <t>الصُّرّة: كيس المتاع</t>
+        </is>
+      </c>
+      <c r="M43" s="7" t="inlineStr"/>
+      <c r="N43" s="7" t="inlineStr"/>
+      <c r="O43" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/51</t>
         </is>
       </c>
     </row>
@@ -2807,45 +3290,56 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>يَصِدُّونَ</t>
+          <t>بِالْطَّاغِيَةِ</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>الزخرف</t>
+          <t>الحاقة</t>
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>يَصِدُّونَ: يَضَجُّونَ، وَيَصِيحُونَ، فَرَحًا، وَجَذَلًا.</t>
+          <t>بِالْطَّاغِيَةِ: أي: بالصَّيحةِ الطَّاغيةِ الَّتي جاوَزَت مِقدارَ الصِّياحِ. والطَّاغي مِن كُلِّ شَيءٍ: ما تجاوَزَ القَدْرَ، وأصلُ (طغي): يدُلُّ على تجاوُزِ الحَدِّ</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>يُعرضون (من الصدود)</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr"/>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/69/1</t>
         </is>
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="inlineStr"/>
+          <t>بِالطَّاغِيَةِ: بِالصَّيْحَةِ الَّتِي جَاوَزَتِ الحَدَّ فِي شِدَّتِهَا.</t>
+        </is>
+      </c>
+      <c r="K44" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/43</t>
+          <t>الحاكم الطاغية المستبد</t>
+        </is>
+      </c>
+      <c r="M44" s="7" t="inlineStr"/>
+      <c r="N44" s="7" t="inlineStr"/>
+      <c r="O44" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/69</t>
         </is>
       </c>
     </row>
@@ -2855,45 +3349,60 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>لَهُمْ شِرْكٌ</t>
+          <t>بَرِقَ</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>الأحقاف</t>
+          <t>القيامة</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>لَهُمْ شِرْكٌ: شِرْكَةٌ وَنَصِيبٌ مَعَ اللهِ تَعَالَى فِي خَلْقِ السَّمَوَاتِ.</t>
+          <t>بَرِقَ: أي: شَخَصَ فلا يَطرِفُ، وفَزِعَ وتحَيَّرَ؛ وبَرَقَ وبَرِقَ: يُقالُ في العَينِ إذا اضطَرَبَتْ وجالتْ مِن خَوفٍ، والإنسانُ إذا بَقِيَ كالمُتَحَيِّرِ قيل: بَرِقَ بَصَرُه بَرَقًا، وأصلُ (برق) هنا: يدُلُّ على لَمعانٍ في شَيءٍ</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>الشرك بالله</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr"/>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/75/2</t>
         </is>
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="inlineStr"/>
+          <t>بَرِقَ الْبَصَرُ: تَحَيَّرَ البَصَرُ وَدُهِشَ لِأَهْوَالِ القِيَامَةِ.</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه في أصل المعنى</t>
+        </is>
+      </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/46</t>
+          <t>لمع البصر</t>
+        </is>
+      </c>
+      <c r="M45" s="7" t="inlineStr"/>
+      <c r="N45" s="7" t="inlineStr">
+        <is>
+          <t>فرق دقيق: الموسوعة تذكر أن أصل (برق) اللمعان، والمراد في الآية الشخوص والتحير</t>
+        </is>
+      </c>
+      <c r="O45" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/75</t>
         </is>
       </c>
     </row>
@@ -2903,45 +3412,60 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>فَنَقَّبُوا</t>
+          <t>سَمْكَهَا</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>ق</t>
+          <t>النازعات</t>
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>فَنَقَّبُوا: طَوَّفُوا.</t>
+          <t>سَمْكَهَا: أي: بِناءَها وسَقْفَها، وأصلُ (سمك): يدُلُّ على عُلُوٍّ</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>حفروا وبحثوا (من التنقيب)</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr"/>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/79/3</t>
         </is>
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="inlineStr"/>
+          <t>رَفَعَ سَمْكَهَا: أَعْلَى سَقْفَهَا.</t>
+        </is>
+      </c>
+      <c r="K46" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/50</t>
+          <t>السُّمك: الكثافة والعَرض</t>
+        </is>
+      </c>
+      <c r="M46" s="7" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="N46" s="7" t="inlineStr"/>
+      <c r="O46" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/79</t>
         </is>
       </c>
     </row>
@@ -2951,45 +3475,68 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>صَرَّةٍ</t>
+          <t>ثَمَّ</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>الذاريات</t>
+          <t>التكوير</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>صَرَّةٍ: صَيْحَةٍ، وَضَجَّةٍ.</t>
+          <t>فَثَمَّ: أي: هنالك</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>الصُّرّة: كيس المتاع</t>
-        </is>
-      </c>
-      <c r="H47" s="7" t="inlineStr"/>
+          <t>غريب الكلمات</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>البقرة 115</t>
+        </is>
+      </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/2/20</t>
         </is>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="inlineStr"/>
+          <t>ثَمَّ: هُنَاكَ فيِ السَّموَاتِ.</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/51</t>
+          <t>ثُمَّ: حرف عطف</t>
+        </is>
+      </c>
+      <c r="M47" s="7" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="N47" s="7" t="inlineStr">
+        <is>
+          <t>شرحته الموسوعة عند البقرة 115 («فَثَمَّ»)</t>
+        </is>
+      </c>
+      <c r="O47" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/81</t>
         </is>
       </c>
     </row>
@@ -2999,45 +3546,60 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>بِالطَّاغِيَةِ</t>
+          <t>يُوعُونَ</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>الحاقة</t>
+          <t>الانشقاق</t>
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>بِالطَّاغِيَةِ: بِالصَّيْحَةِ الَّتِي جَاوَزَتِ الحَدَّ فِي شِدَّتِهَا.</t>
+          <t>يُوعُونَ: أي: يَكتُمونَ ويَجمَعونَ في صُدورِهم مِنَ الكُفرِ والتَّكذيبِ، وأصلُ (وعي): يدُلُّ على ضَمِّ شَيءٍ</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>الحاكم الطاغية المستبد</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr"/>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/84/3</t>
         </is>
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="inlineStr"/>
+          <t>يُوعُونَ: يَكْتُمُونَ فيِ صُدُورِهِمْ مِنَ العِنَادِ، وَالتَّكْذِيبِ.</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/69</t>
+          <t>من الوعي والإدراك</t>
+        </is>
+      </c>
+      <c r="M48" s="7" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="N48" s="7" t="inlineStr"/>
+      <c r="O48" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/84</t>
         </is>
       </c>
     </row>
@@ -3047,45 +3609,60 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>بَرِقَ الْبَصَرُ</t>
+          <t>جَابُوا الصَّخْرَ</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>القيامة</t>
+          <t>الفجر</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>بَرِقَ الْبَصَرُ: تَحَيَّرَ البَصَرُ وَدُهِشَ لِأَهْوَالِ القِيَامَةِ.</t>
+          <t>جَابُوا الصَّخْرَ: أي: قَطَعوا صَخرَ الجِبالِ، واتَّخَذوا فيها بُيُوتًا نَحَتوها مِنَ الصَّخرِ، والجَوْبُ: القَطعُ، تقولُ: جُبتُ البِلادَ أَجوبُها: إذا قطَعْتَها، ومنه الجَوابُ؛ لأنَّه يَقطَعُ السُّؤالَ، وأصلُ (جوب): يدُلُّ على خَرقِ الشَّيءِ</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>لمع البصر</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr"/>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>عالية: نسختان خام متطابقتان</t>
+          <t>https://dorar.net/tafseer/89/1</t>
         </is>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="inlineStr"/>
+          <t>جَابُوا: قَطَعُوا.</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/75</t>
+          <t>جلبوا الصخر وأحضروه</t>
+        </is>
+      </c>
+      <c r="M49" s="7" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="N49" s="7" t="inlineStr"/>
+      <c r="O49" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/89</t>
         </is>
       </c>
     </row>
@@ -3095,49 +3672,60 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>رَفَعَ سَمْكَهَا</t>
+          <t>فَقَدَرَ</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>النازعات</t>
+          <t>الفجر</t>
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>رَفَعَ سَمْكَهَا: أَعْلَى سَقْفَهَا.</t>
+          <t>فَقَدَرَ: أي: ضيَّق، فلم يُكْثِرْ مالَه، ولم يُوَسِّعْ عليه، يقال: قَدَرْتُ عليه الشَّيءَ: ضيَّقْتُه، كأنَّما جعَلْته بقَدْرٍ، وقُدِر عليه الرِّزقُ، أي: أُعْطِيَ ذلك بقَدْرٍ يَسِيرٍ، وأصلُ (قدر): يدُلُّ على مَبْلَغِ الشَّيءِ وكُنْهِه ونِهايَتِه</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>السُّمك: الكثافة والعَرض</t>
-        </is>
-      </c>
-      <c r="H50" s="7" t="inlineStr">
+          <t>غريب الكلمات</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr"/>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>https://dorar.net/tafseer/89/2</t>
+        </is>
+      </c>
+      <c r="J50" s="7" t="inlineStr">
+        <is>
+          <t>فَقَدَرَ: ضَيَّقَ.</t>
+        </is>
+      </c>
+      <c r="K50" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
+      <c r="L50" s="7" t="inlineStr">
+        <is>
+          <t>من القدرة والاستطاعة</t>
+        </is>
+      </c>
+      <c r="M50" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="I50" s="7" t="inlineStr">
-        <is>
-          <t>عالية: نسختان خام متطابقتان</t>
-        </is>
-      </c>
-      <c r="J50" s="7" t="inlineStr">
-        <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K50" s="7" t="inlineStr"/>
-      <c r="L50" s="7" t="inlineStr">
-        <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/79</t>
+      <c r="N50" s="7" t="inlineStr"/>
+      <c r="O50" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/89</t>
         </is>
       </c>
     </row>
@@ -3147,53 +3735,60 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>ثَمَّ</t>
+          <t>مَمْنُونٍ</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>التكوير</t>
+          <t>التين</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>ثَمَّ: هُنَاكَ فيِ السَّموَاتِ.</t>
+          <t>مَمْنُونٍ: أي: مَقطوعٍ مَنقوصٍ، وأصلُ (منن) هنا: يدُلُّ على قَطْعٍ</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>ثُمَّ: حرف عطف</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr">
+          <t>غريب الكلمات</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr"/>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>https://dorar.net/tafseer/95/1</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>غَيْرُ مَمْنُونٍ: غَيْرُ مَقْطُوعٍ، وَلَا مَنْقُوصٍ.</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>بلا مِنّة</t>
+        </is>
+      </c>
+      <c r="M51" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="I51" s="7" t="inlineStr">
-        <is>
-          <t>عالية: نسختان خام متطابقتان</t>
-        </is>
-      </c>
-      <c r="J51" s="7" t="inlineStr">
-        <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="inlineStr">
-        <is>
-          <t>في قوله: مطاع ثم أمين. الخطأ في قراءة الحركة يقلب المعنى</t>
-        </is>
-      </c>
-      <c r="L51" s="7" t="inlineStr">
-        <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/81</t>
+      <c r="N51" s="7" t="inlineStr"/>
+      <c r="O51" s="7" t="inlineStr">
+        <is>
+          <t>https://quranenc.com/ar/browse/arabic_seraj/95</t>
         </is>
       </c>
     </row>
@@ -3203,262 +3798,69 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>يُوعُونَ</t>
+          <t>فَأُمُّهُ هَاوِيَةٌ</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>الانشقاق</t>
+          <t>القارعة</t>
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>يُوعُونَ: يَكْتُمُونَ فيِ صُدُورِهِمْ مِنَ العِنَادِ، وَالتَّكْذِيبِ.</t>
+          <t>أي: فمَأْواه ومَسكَنُه في مَوضِعٍ بَعيدٍ قَعْرُه، يَهْوِي فيه على رأسِه</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>من الوعي والإدراك</t>
-        </is>
-      </c>
-      <c r="H52" s="7" t="inlineStr">
+          <t>تفسير الآيات</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr"/>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>https://dorar.net/tafseer/101/1</t>
+        </is>
+      </c>
+      <c r="J52" s="7" t="inlineStr">
+        <is>
+          <t>فَأُمُّهُ هَاوِيَةٌ: مَاوَاهُ إِلَى جَهَنَّمَ يَهْوِي عَلَى رَاسِهِ.</t>
+        </is>
+      </c>
+      <c r="K52" s="7" t="inlineStr">
+        <is>
+          <t>يوافقه</t>
+        </is>
+      </c>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>أمّه: والدته</t>
+        </is>
+      </c>
+      <c r="M52" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="I52" s="7" t="inlineStr">
-        <is>
-          <t>عالية: نسختان خام متطابقتان</t>
-        </is>
-      </c>
-      <c r="J52" s="7" t="inlineStr">
-        <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="inlineStr"/>
-      <c r="L52" s="7" t="inlineStr">
-        <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/84</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>جَابُوا</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>الفجر</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="n">
-        <v>89</v>
-      </c>
-      <c r="E53" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>جَابُوا: قَطَعُوا.</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>جلبوا الصخر وأحضروه</t>
-        </is>
-      </c>
-      <c r="H53" s="7" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I53" s="7" t="inlineStr">
-        <is>
-          <t>عالية: نسختان خام متطابقتان</t>
-        </is>
-      </c>
-      <c r="J53" s="7" t="inlineStr">
-        <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="inlineStr"/>
-      <c r="L53" s="7" t="inlineStr">
-        <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/89</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>فَقَدَرَ</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>الفجر</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="n">
-        <v>89</v>
-      </c>
-      <c r="E54" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>فَقَدَرَ: ضَيَّقَ.</t>
-        </is>
-      </c>
-      <c r="G54" s="7" t="inlineStr">
-        <is>
-          <t>من القدرة والاستطاعة</t>
-        </is>
-      </c>
-      <c r="H54" s="7" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I54" s="7" t="inlineStr">
-        <is>
-          <t>عالية: نسختان خام متطابقتان</t>
-        </is>
-      </c>
-      <c r="J54" s="7" t="inlineStr">
-        <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K54" s="7" t="inlineStr"/>
-      <c r="L54" s="7" t="inlineStr">
-        <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/89</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>غَيْرُ مَمْنُونٍ</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>التين</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="n">
-        <v>95</v>
-      </c>
-      <c r="E55" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>غَيْرُ مَمْنُونٍ: غَيْرُ مَقْطُوعٍ، وَلَا مَنْقُوصٍ.</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>بلا مِنّة</t>
-        </is>
-      </c>
-      <c r="H55" s="7" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I55" s="8" t="inlineStr">
-        <is>
-          <t>تحتاج مطابقة: «مقطوع» في 3 نسخ و«مقطع» في نسختين</t>
-        </is>
-      </c>
-      <c r="J55" s="7" t="inlineStr">
-        <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K55" s="7" t="inlineStr"/>
-      <c r="L55" s="7" t="inlineStr">
-        <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/95</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>فَأُمُّهُ هَاوِيَةٌ</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>القارعة</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="n">
-        <v>101</v>
-      </c>
-      <c r="E56" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="F56" s="7" t="inlineStr">
-        <is>
-          <t>فَأُمُّهُ هَاوِيَةٌ: مَاوَاهُ إِلَى جَهَنَّمَ يَهْوِي عَلَى رَاسِهِ.</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="inlineStr">
-        <is>
-          <t>أمّه: والدته</t>
-        </is>
-      </c>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I56" s="7" t="inlineStr">
-        <is>
-          <t>عالية: نسختان خام متطابقتان</t>
-        </is>
-      </c>
-      <c r="J56" s="7" t="inlineStr">
-        <is>
-          <t>قائمة الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهمها</t>
-        </is>
-      </c>
-      <c r="K56" s="7" t="inlineStr"/>
-      <c r="L56" s="7" t="inlineStr">
+      <c r="N52" s="7" t="inlineStr">
+        <is>
+          <t>نص «غريب الكلمات» يشرح «هاوية» وحدها، فنُقلت جملة «تفسير الآيات» لأنها تشرح «فأمه» أيضاً</t>
+        </is>
+      </c>
+      <c r="O52" s="7" t="inlineStr">
         <is>
           <t>https://quranenc.com/ar/browse/arabic_seraj/101</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L56"/>
+  <autoFilter ref="A1:O52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3473,15 +3875,15 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3497,22 +3899,22 @@
       </c>
       <c r="C1" s="5" t="inlineStr">
         <is>
-          <t>رقم الحديث في HadeethEnc</t>
+          <t>التخريج في الصحيحين (الموسوعة الحديثية — الدرر السنية)</t>
         </is>
       </c>
       <c r="D1" s="5" t="inlineStr">
         <is>
-          <t>نص الحديث (منقول بنصه)</t>
+          <t>رابط الموسوعة الحديثية</t>
         </is>
       </c>
       <c r="E1" s="5" t="inlineStr">
         <is>
-          <t>التخريج</t>
+          <t>نص الحديث (منقول بنصه من HadeethEnc)</t>
         </is>
       </c>
       <c r="F1" s="5" t="inlineStr">
         <is>
-          <t>الدرجة</t>
+          <t>في HadeethEnc</t>
         </is>
       </c>
       <c r="G1" s="5" t="inlineStr">
@@ -3532,7 +3934,7 @@
       </c>
       <c r="J1" s="5" t="inlineStr">
         <is>
-          <t>الرابط</t>
+          <t>رابط HadeethEnc</t>
         </is>
       </c>
     </row>
@@ -3547,22 +3949,22 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>6454</t>
+          <t>صحيح مسلم (2581)</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
+          <t>https://dorar.net/h/kwlXLxcl</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
           <t>عَنْ أَبِي هُرَيْرَةَ رضي الله عنه أَنَّ رَسُولَ اللهِ صَلَّى اللهُ عَلَيْهِ وَسَلَّمَ قَالَ: «أَتَدْرُونَ مَا الْمُفْلِسُ؟» قَالُوا: الْمُفْلِسُ فِينَا مَنْ لَا دِرْهَمَ لَهُ وَلَا مَتَاعَ، فَقَالَ: «إِنَّ الْمُفْلِسَ مِنْ أُمَّتِي يَأْتِي يَوْمَ الْقِيَامَةِ بِصَلَاةٍ وَصِيَامٍ وَزَكَاةٍ، وَيَأْتِي قَدْ شَتَمَ هَذَا، وَقَذَفَ هَذَا، وَأَكَلَ مَالَ هَذَا، وَسَفَكَ دَمَ هَذَا، وَضَرَبَ هَذَا، فَيُعْطَى هَذَا مِنْ حَسَنَاتِهِ، وَهَذَا مِنْ حَسَنَاتِهِ، فَإِنْ فَنِيَتْ حَسَنَاتُهُ قَبْلَ أَنْ يُقْضَى مَا عَلَيْهِ أُخِذَ مِنْ خَطَايَاهُمْ فَطُرِحَتْ عَلَيْهِ، ثُمَّ طُرِحَ فِي النَّارِ».</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>رواه مسلم</t>
-        </is>
-      </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>صحيح</t>
+          <t>HadeethEnc رقم 6454: رواه مسلم، صحيح</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
@@ -3575,7 +3977,7 @@
           <t>يأتي يوم القيامة بحسنات ثم تؤخذ منه لمن ظلمهم (من نص الحديث)</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr"/>
+      <c r="I2" s="7" t="n"/>
       <c r="J2" s="7" t="inlineStr">
         <is>
           <t>https://hadeethenc.com/ar/browse/hadith/6454</t>
@@ -3593,22 +3995,22 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>صحيح البخاري (6114)؛ صحيح مسلم (2609)</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
+          <t>https://dorar.net/h/SllC88XC</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
           <t>عن أبي هريرة رضي الله عنه أن رسول الله صلى الله عليه وسلم قال: «لَيْسَ الشَّدِيدُ بِالصُّرَعَةِ، إِنَّمَا الشَّدِيدُ الَّذِي يَمْلِكُ نَفْسَهُ عِنْدَ الْغَضَبِ».</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>متفق عليه</t>
-        </is>
-      </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>صحيح</t>
+          <t>HadeethEnc رقم 5351: متفق عليه، صحيح</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
@@ -3621,7 +4023,7 @@
           <t>الشديد: الذي يملك نفسه عند الغضب (من نص الحديث)</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr"/>
+      <c r="I3" s="7" t="n"/>
       <c r="J3" s="7" t="inlineStr">
         <is>
           <t>https://hadeethenc.com/ar/browse/hadith/5351</t>
@@ -3639,22 +4041,22 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>صحيح البخاري (6446)؛ صحيح مسلم (1051)</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>https://dorar.net/h/yT26X1Vz</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
           <t>عن أبي هريرة رضي الله عنه عن النبي صلى الله عليه وسلم قال: «ليس الغِنَى عن كَثرَة العَرَض، ولكن الغِنَى غنى النفس».</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>متفق عليه</t>
-        </is>
-      </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>صحيح</t>
+          <t>HadeethEnc رقم 3852: متفق عليه، صحيح</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -3689,22 +4091,22 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>10101</t>
+          <t>صحيح البخاري (10)؛ صحيح البخاري (6484)</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
+          <t>https://dorar.net/h/9itq9NoB</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
           <t>عَنْ عَبْدِ اللَّهِ بْنِ عَمْرٍو رَضِيَ اللَّهُ عَنْهُمَا عَنِ النَّبِيِّ صَلَّى اللهُ عَلَيْهِ وَسَلَّمَ قَالَ: «المُسْلِمُ مَنْ سَلِمَ المُسْلِمُونَ مِنْ لِسَانِهِ وَيَدِهِ، وَالمُهَاجِرُ مَنْ هَجَرَ مَا نَهَى اللَّهُ عَنْهُ».</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>متفق عليه</t>
-        </is>
-      </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>صحيح</t>
+          <t>HadeethEnc رقم 10101: متفق عليه، صحيح</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -3717,7 +4119,7 @@
           <t>المسلم: من سلم المسلمون من لسانه ويده؛ والمهاجر: من هجر ما نهى الله عنه (من نص الحديث)</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="n"/>
       <c r="J5" s="7" t="inlineStr">
         <is>
           <t>https://hadeethenc.com/ar/browse/hadith/10101</t>
@@ -3736,17 +4138,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3757,7 +4161,7 @@
       </c>
       <c r="B1" s="5" t="inlineStr">
         <is>
-          <t>اللفظ (للبحث فقط؛ النص القرآني يؤخذ من المصحف)</t>
+          <t>اللفظ (للبحث فقط)</t>
         </is>
       </c>
       <c r="C1" s="5" t="inlineStr">
@@ -3777,17 +4181,27 @@
       </c>
       <c r="F1" s="5" t="inlineStr">
         <is>
-          <t>ما في «السراج» لهذه الآية (منقول بنصه)</t>
+          <t>تشرحه موسوعة التفسير؟</t>
         </is>
       </c>
       <c r="G1" s="5" t="inlineStr">
         <is>
-          <t>السلوك المتوقع من النظام</t>
+          <t>قسم الموسوعة</t>
         </is>
       </c>
       <c r="H1" s="5" t="inlineStr">
         <is>
-          <t>الرابط</t>
+          <t>رابط الموسوعة</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>في «السراج»</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>السلوك المتوقع من التطبيق</t>
         </is>
       </c>
     </row>
@@ -3813,17 +4227,27 @@
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>(لا شرح في هذه الآية)</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>يمتنع النظام عن الحكم، ويعرض نص المصدر كما هو</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/75</t>
+          <t>https://dorar.net/tafseer/75/1</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>لا شرح للفظ في هذا الموضع</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>يمتنع التطبيق عن الحكم لأن اللفظ ليس في قائمته، ولا يولّد معنى</t>
         </is>
       </c>
     </row>
@@ -3849,18 +4273,27 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>وَلَا تُخَافِتْ بِهَا: ولَا تُسِرَّ بِهَا.
-وَابْتَغِ بَيْنَ ذَلِكَ سَبِيلًا: كُنْ وَسَطًا في القِرَاءَةِ بَيْنَ الجَهْرِ، وَالمُخَافَتَةِ.</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>يمتنع النظام عن الحكم، ويعرض نص المصدر كما هو</t>
+          <t>المعنى الإجمالي</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/17</t>
+          <t>https://dorar.net/tafseer/17/26</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>لا شرح للفظ في هذا الموضع</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>يمتنع التطبيق عن الحكم لأن اللفظ ليس في قائمته، ولا يولّد معنى</t>
         </is>
       </c>
     </row>
@@ -3886,18 +4319,27 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>تُرِيحُونَ: تَرُدُّونَهَا إِلَى مَبَارِكِهَا وَحَظَائِرِهَا فِي المَسَاءِ.
-تَسْرَحُونَ: تُخْرِجُونَهَا لِلْمَرْعَى فِي الصَّبَاحِ.</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>يمتنع النظام عن الحكم، ويعرض نص المصدر كما هو</t>
+          <t>تفسير الآيات</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/16</t>
+          <t>https://dorar.net/tafseer/16/2</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>لا شرح للفظ في هذا الموضع</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>يمتنع التطبيق عن الحكم لأن اللفظ ليس في قائمته، ولا يولّد معنى</t>
         </is>
       </c>
     </row>
@@ -3923,17 +4365,27 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>(لا شرح في هذه الآية)</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>يمتنع النظام عن الحكم، ويعرض نص المصدر كما هو</t>
+          <t>تفسير الآيات</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/12</t>
+          <t>https://dorar.net/tafseer/12/14</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>لا شرح للفظ في هذا الموضع</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>يمتنع التطبيق عن الحكم لأن اللفظ ليس في قائمته، ولا يولّد معنى</t>
         </is>
       </c>
     </row>
@@ -3959,17 +4411,27 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>(لا شرح في هذه الآية)</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>يمتنع النظام عن الحكم، ويعرض نص المصدر كما هو</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/6</t>
+          <t>https://dorar.net/tafseer/6/41</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>لا شرح للفظ في هذا الموضع</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>يمتنع التطبيق عن الحكم لأن اللفظ ليس في قائمته، ولا يولّد معنى</t>
         </is>
       </c>
     </row>
@@ -3995,17 +4457,27 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>(لا شرح في هذه الآية)</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>يمتنع النظام عن الحكم، ويعرض نص المصدر كما هو</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/4</t>
+          <t>https://dorar.net/tafseer/4/23</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>لا شرح للفظ في هذا الموضع</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>يمتنع التطبيق عن الحكم لأن اللفظ ليس في قائمته، ولا يولّد معنى</t>
         </is>
       </c>
     </row>
@@ -4031,17 +4503,27 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>(لا شرح في هذه الآية)</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>يمتنع النظام عن الحكم، ويعرض نص المصدر كما هو</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/4</t>
+          <t>https://dorar.net/tafseer/4/14</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>لا شرح للفظ في هذا الموضع</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>يمتنع التطبيق عن الحكم لأن اللفظ ليس في قائمته، ولا يولّد معنى</t>
         </is>
       </c>
     </row>
@@ -4067,17 +4549,27 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>(لا شرح في هذه الآية)</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>يمتنع النظام عن الحكم، ويعرض نص المصدر كما هو</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/2</t>
+          <t>https://dorar.net/tafseer/2/37</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>لا شرح للفظ في هذا الموضع</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>يمتنع التطبيق عن الحكم لأن اللفظ ليس في قائمته، ولا يولّد معنى</t>
         </is>
       </c>
     </row>
@@ -4103,17 +4595,27 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>(لا شرح في هذه الآية)</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>يمتنع النظام عن الحكم، ويعرض نص المصدر كما هو</t>
+          <t>تفسير الآيات</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/2</t>
+          <t>https://dorar.net/tafseer/2/24</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>لا شرح للفظ في هذا الموضع</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>يمتنع التطبيق عن الحكم لأن اللفظ ليس في قائمته، ولا يولّد معنى</t>
         </is>
       </c>
     </row>
@@ -4139,17 +4641,27 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>(لا شرح في هذه الآية)</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>يمتنع النظام عن الحكم، ويعرض نص المصدر كما هو</t>
+          <t>تفسير الآيات</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/2</t>
+          <t>https://dorar.net/tafseer/2/24</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>لا شرح للفظ في هذا الموضع</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>يمتنع التطبيق عن الحكم لأن اللفظ ليس في قائمته، ولا يولّد معنى</t>
         </is>
       </c>
     </row>
@@ -4175,17 +4687,27 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>(لا شرح في هذه الآية)</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>يمتنع النظام عن الحكم، ويعرض نص المصدر كما هو</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/2</t>
+          <t>https://dorar.net/tafseer/2/9</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>لا شرح للفظ في هذا الموضع</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>يمتنع التطبيق عن الحكم لأن اللفظ ليس في قائمته، ولا يولّد معنى</t>
         </is>
       </c>
     </row>
@@ -4211,17 +4733,27 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>حَاشِرِينَ: جَامِعِينَ لِلْجَيْشِ مِنَ المَدَائِنِ.</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>يمتنع النظام عن الحكم، ويعرض نص المصدر كما هو</t>
+          <t>تفسير الآيات</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/26</t>
+          <t>https://dorar.net/tafseer/26/5</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>لا شرح للفظ في هذا الموضع</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>يمتنع التطبيق عن الحكم لأن اللفظ ليس في قائمته، ولا يولّد معنى</t>
         </is>
       </c>
     </row>
@@ -4247,23 +4779,32 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>تَكُ: تَكُنْ.
-لَّدُنْهُ: عِنْدَهُ.</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>يمتنع النظام عن الحكم، ويعرض نص المصدر كما هو</t>
+          <t>غريب الكلمات</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj/4</t>
+          <t>https://dorar.net/tafseer/4/13</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>لا شرح للفظ في هذا الموضع</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>يمتنع التطبيق عن الحكم لأن اللفظ ليس في قائمته، ولا يولّد معنى</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H14"/>
+  <autoFilter ref="A1:J14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4274,14 +4815,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4520,8 +5061,100 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>التَّهْلُكَة</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>البقرة</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>195</v>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>معنى الموسوعة («الهلاك») لا يؤيد أن الفهم الشائع («الخطر عموماً») خطأ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>سُكِّرَتْ</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>الحجر</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>خالف «السراج» («سُحِرَتْ») موسوعةَ التفسير («سُدَّتْ، ومُنِعَت النَّظَرَ»)؛ فاستُبعد وفق القاعدة الرابعة</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>نَافِلَةً لَّكَ</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>الإسراء</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>معنى الموسوعة («زيادةً؛ مِن النَّفلِ: وهو الزِّيادةُ على الواجِبِ») لا يؤيد أن الفهم الشائع خطأ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>وَجِلَةٌ</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>المؤمنون</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>معنى الموسوعة («خائِفةٌ») لا يؤيد أن الفهم الشائع («خائفة من ذنوبها») خطأ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E10"/>
+  <autoFilter ref="A1:E14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4532,14 +5165,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
     <col width="90" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4555,7 +5188,7 @@
       </c>
       <c r="C1" s="5" t="inlineStr">
         <is>
-          <t>الوصف / النص</t>
+          <t>الوصف والشروط</t>
         </is>
       </c>
       <c r="D1" s="5" t="inlineStr">
@@ -4575,22 +5208,18 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>السراج في بيان غريب القرآن</t>
+          <t>موسوعة التفسير (الدرر السنية) — المصدر الأساسي للمعنى</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>QuranEnc — اللغة العربية: معاني الكلمات (المفتاح arabic_seraj)</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>V1.0.0 (تاريخ الإصدار المرجّح 17/12/2025، يُتحقق منه في الموقع)</t>
-        </is>
-      </c>
+          <t>من المرجعية العلمية المعتمدة في «الحزمة العلمية» للتحدي (التفسير: dorar.net/tafseer). يُنقل نص «غريب الكلمات»، أو جملة «تفسير الآيات» عند غيابه.</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr"/>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/browse/arabic_seraj</t>
+          <t>https://dorar.net/tafseer</t>
         </is>
       </c>
     </row>
@@ -4600,18 +5229,22 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>شروط QuranEnc</t>
+          <t>السراج في بيان غريب القرآن (QuranEnc) — للموافقة</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>1. عدم التعديل أو الإضافة أو الحذف على المحتوى. 2. الإشارة بوضوح للناشر وللمصدر (QuranEnc.com). 3. ذكر رقم الإصدار عند إعادة نشر الترجمة. 4. إبقاء معلومات نسخة الترجمة الموجودة داخل المستند. 5. إفادة المصدر بأي ملاحظة على الترجمة. 6. تطوير الترجمات وفق النسخ الجديدة الصادرة من المصدر. 7. عدم تضمين إعلانات لا تليق بترجمات معاني القرآن الكريم عند العرض.</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr"/>
+          <t>يُعرض تحت معنى الموسوعة ما يوافقه في «السراج». شروط QuranEnc: عدم التعديل أو الإضافة أو الحذف، والإشارة إلى الناشر والمصدر، وذكر رقم الإصدار.</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>V1.0.0</t>
+        </is>
+      </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>https://quranenc.com/ar/home/api/</t>
+          <t>https://quranenc.com/ar/browse/arabic_seraj</t>
         </is>
       </c>
     </row>
@@ -4621,18 +5254,18 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>موسوعة الأحاديث النبوية</t>
+          <t>الموسوعة الحديثية (الدرر السنية)</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>HadeethEnc — نص الحديث ودرجته وتخريجه</t>
+          <t>تخريج الأحاديث في الصحيحين، من المرجعية المعتمدة في الحزمة (الحديث: الصحيحان، dorar.net/hadith).</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr"/>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>https://hadeethenc.com/ar/home</t>
+          <t>https://dorar.net/hadith</t>
         </is>
       </c>
     </row>
@@ -4642,18 +5275,18 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>قائمة الألفاظ الشائع خطأ فهمها</t>
+          <t>موسوعة الأحاديث النبوية (HadeethEnc)</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>الكلم الطيب: كلمات في القرآن يشيع الخطأ في فهم معناها إلى معنى دارج (استُعملت فهرساً لاختيار الألفاظ فقط)</t>
+          <t>نص الحديث ودرجته. شروطها: عدم التعديل، والإشارة إلى الناشر والمصدر، وذكر رقم الإصدار.</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr"/>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>https://kalemtayeb.com/quran/sub/2660</t>
+          <t>https://hadeethenc.com/ar/home</t>
         </is>
       </c>
     </row>
@@ -4663,19 +5296,40 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>طريقة النقل</t>
+          <t>نص القرآن الكريم</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>جُلب كل معنى من واجهة QuranEnc البرمجية، ونُقل النص من الرموز الخام مرتين ثم قورن. الألفاظ التي لم يشرحها المصدر نُقلت إلى «حالات الامتناع» ولم يُكتب لها معنى من خارج المصدر.</t>
+          <t>برسم طبعة مجمع الملك فهد، كما تشترط الحزمة العلمية (يُضاف في التطبيق).</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="7" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>قائمة الألفاظ الشائع خطأ فهمها</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>الكلم الطيب: فهرس لاختيار الألفاظ فقط.</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>https://kalemtayeb.com/quran/sub/2660</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E6"/>
+  <autoFilter ref="A1:E7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/قائمة-الألفاظ-بل.xlsx
+++ b/قائمة-الألفاظ-بل.xlsx
@@ -1323,7 +1323,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>أَقَلَّتْ: أي: حمَلَتْ؛ يُقال: أقلَ فلَانٌ الشَّيْءَ واستقلَّ به: إذا أطاقَه وحمَلَه، وأقْلَلْت كذا: وجدتَه قليلَ المحمَلِ أي: خفيفًا، وأصلُ (قلل): يدلُّ على نَزارةِ الشَّيءِ، وعلى الانزعاجِ الذي هو خِلافُ الاستقرارِ</t>
+          <t>أَقَلَّتْ: أي: حمَلَتْ؛ يُقال: أقلَّ فلَانٌ الشَّيْءَ واستقلَّ به: إذا أطاقَه وحمَلَه، وأقْلَلْت كذا: وجدتَه قليلَ المحمَلِ أي: خفيفًا، وأصلُ (قلل): يدلُّ على نَزارةِ الشَّيءِ، وعلى الانزعاجِ الذي هو خِلافُ الاستقرارِ</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>فَقَدَرَ: أي: ضيَّق، فلم يُكْثِرْ مالَه، ولم يُوَسِّعْ عليه، يقال: قَدَرْتُ عليه الشَّيءَ: ضيَّقْتُه، كأنَّما جعَلْته بقَدْرٍ، وقُدِر عليه الرِّزقُ، أي: أُعْطِيَ ذلك بقَدْرٍ يَسِيرٍ، وأصلُ (قدر): يدُلُّ على مَبْلَغِ الشَّيءِ وكُنْهِه ونِهايَتِه</t>
+          <t>فَقَدَرَ: أي: ضيَّق، فلم يُكْثِرْ مالَه، ولم يُوَسِّعْ عليه، يقال: قَدَرْتُ عليه الشَّيءَ: ضيَّقْتُه، كأنَّما جعَلْته بقَدرٍ، وقُدِر عليه الرِّزقُ، أي: أُعْطِيَ ذلك بقَدْرٍ يَسِيرٍ، وأصلُ (قدر): يدُلُّ على مَبْلَغِ الشَّيءِ وكُنْهِه ونِهايَتِه</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>من المرجعية العلمية المعتمدة في «الحزمة العلمية» للتحدي (التفسير: dorar.net/tafseer). يُنقل نص «غريب الكلمات»، أو جملة «تفسير الآيات» عند غيابه.</t>
+          <t>من المرجعية العلمية المعتمدة في «الحزمة العلمية» للتحدي (التفسير: dorar.net/tafseer). يُنقل نص «غريب الكلمات»، أو جملة من «تفسير الآيات» أو «المعنى الإجمالي» عند غيابه.</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr"/>
